--- a/02_加值成品/九上/九上7-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-1 地球的運動　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上7-1 地球的運動　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>地球繞地軸旋轉是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>自轉</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>視運動</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>晝夜</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>旋轉</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>地球自轉約多久一圈？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>視運動</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>約23.5度</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>公轉</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>24小時</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>一天</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>地球繞太陽運行是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>公轉</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>晝夜</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>視運動</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>自轉</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>繞日</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>地球公轉約多久一圈？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>一年</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>地軸傾斜</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>公轉</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>自轉</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>約365天</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>晝夜交替是什麼造成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>自轉</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>長</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>旋轉</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>四季變化主要因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>地軸傾斜加公轉</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>無正常晝夜交替</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>太陽直射北半球晝最長</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>自轉使一面向陽一面背陽</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>傾斜</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>太陽東升西落是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>視運動</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>自轉</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>自轉造成</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>地球自轉方向？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>由西向東</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>晝夜</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>地軸傾斜</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>幾乎沒有</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>自轉</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>晝夜交替是地球哪種運動造成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>自轉</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>視運動</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>晝夜</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>地軸傾斜</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>旋轉</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>四季是地球公轉加什麼造成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>地軸傾斜</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>由西向東</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>傾斜</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-1 地球的運動　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上7-1 地球的運動　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>向陽的一面是白天還黑夜？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>公轉</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>自轉</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>受光</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>四季是離太陽遠近造成嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>視運動</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>幾乎沒有</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>地軸傾斜</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>夏季白天通常較？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>長</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>晝長</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>冬季白天通常較？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>短</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>自轉</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>地軸傾斜</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>幾乎沒有</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>晝短</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>太陽視運動由東到西因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>地球由西向東自轉</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>實為地球自轉造成的相對移動</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>幾乎沒有明顯四季</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>地軸傾斜加公轉</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>相對</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>若地軸不傾斜還有四季嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>幾乎沒有明顯四季</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>無正常晝夜交替</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>自轉定晝夜、公轉加傾斜定季節日照</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>地軸傾斜加公轉</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>傾斜關鍵</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>自轉造成的是晝夜還四季？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>實為地球自轉</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>視運動</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>晝夜</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>旋轉</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>公轉造成的是晝夜還四季？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>地球由西向東自轉</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>太陽直射北半球晝最長</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>四季(配合傾斜)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>地軸傾斜使公轉時太陽直射位置變,受熱不均成四季</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>繞日</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>地球自轉一圈約需？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>幾乎沒有明顯四季</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>實為地球自轉造成的相對移動</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>24小時</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>一天</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>北半球夏季白天較長還短？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>公轉</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>視運動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>晝夜</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>長</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>晝長</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-1 地球的運動　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上7-1 地球的運動　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明四季形成的完整原因？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>高緯較明顯赤道較不明顯</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>自轉定晝夜、公轉加傾斜定季節日照</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>地軸傾斜使公轉時太陽直射位置變,受熱不均成四季</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>地軸傾斜加公轉</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何說太陽東升西落是視運動？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>實為地球自轉造成的相對移動</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>幾乎沒有明顯四季</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>自轉使一面向陽一面背陽</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>地軸傾斜加公轉</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>相對</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>夏至白天最長的原因？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>幾乎沒有明顯四季</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>無正常晝夜交替</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>四季(配合傾斜)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>太陽直射北半球晝最長</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>季節</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>同一時刻地球兩側為何一晝一夜？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>地球由西向東自轉</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>自轉使一面向陽一面背陽</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>太陽直射北半球晝最長</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>地軸傾斜加公轉</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>自轉</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>不同緯度四季分明程度差異？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>四季(配合傾斜)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>高緯較明顯赤道較不明顯</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>實為地球自轉造成的相對移動</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>地軸傾斜加公轉</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>緯度</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>地軸傾斜約幾度影響四季？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>約23.5度</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>無正常晝夜交替</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>太陽直射北半球晝最長</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>傾角</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>若地球不自轉會如何？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>地軸傾斜使公轉時太陽直射位置變,受熱不均成四季</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>實為地球自轉造成的相對移動</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>四季(配合傾斜)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>無正常晝夜交替</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>假設</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>公轉與自轉如何共同影響日照？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>地球由西向東自轉</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>地軸傾斜使公轉時太陽直射位置變,受熱不均成四季</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>自轉定晝夜、公轉加傾斜定季節日照</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>四季(配合傾斜)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>若地軸不傾斜還會有明顯四季嗎？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>幾乎沒有</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>自轉</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>長</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>傾斜關鍵</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何日出日落是太陽的視運動？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>實為地球自轉</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>一年</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>長</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>相對</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上7-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>旋轉</t>
+          <t>旋轉：地球繞著自己中心的一條假想軸(地軸)不停旋轉，這個運動稱為自轉</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>一天</t>
+          <t>一天：地球自轉一圈所需的時間大約是24小時，這就是我們所定義的一天</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>繞日</t>
+          <t>繞日：地球繞著太陽運行的運動稱為公轉</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>約365天</t>
+          <t>約365天：地球繞太陽公轉一圈所需的時間大約是365天，這就是我們所定義的一年</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>旋轉</t>
+          <t>旋轉：地球不停自轉，面向太陽的一面是白天、背向太陽的一面是黑夜，因此產生晝夜交替</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>傾斜</t>
+          <t>傾斜：地球一邊繞太陽公轉、地軸又傾斜一定角度，使得不同季節裡陽光照射地表的角度和時間長短不同，因此形成四季</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>自轉造成</t>
+          <t>自轉造成：其實是地球自轉，並不是太陽真的繞著地球跑，但站在地面上的我們感覺像是太陽在天空中由東向西移動，這種因觀察者運動造成的錯覺稱為視運動</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>自轉</t>
+          <t>自轉：地球自轉的方向是由西向東，因此我們才會看到太陽、月亮等星體視運動上呈現由東向西移動</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>旋轉</t>
+          <t>旋轉：地球繞著自己的地軸不停自轉,面向太陽的一面是白天、背向太陽的一面是黑夜,因此產生晝夜交替</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>傾斜</t>
+          <t>傾斜：地球一邊繞太陽公轉、地軸又傾斜一定角度,使得不同季節裡陽光照射地表的角度和時間長短不同,因此形成四季</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>受光</t>
+          <t>受光：地球面向太陽、能接受到陽光照射的一面是白天，背向太陽照不到陽光的一面則是黑夜</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>地軸傾斜</t>
+          <t>地軸傾斜：地球和太陽的距離全年變化很小，並非造成四季的主要原因；真正的原因是地軸傾斜，使不同季節太陽直射地表的角度不同</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>晝長</t>
+          <t>晝長：北半球夏季時，地軸傾向太陽的那一側白天較長、黑夜較短</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>晝短</t>
+          <t>晝短：北半球冬季時，地軸傾離太陽的那一側白天較短、黑夜較長</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>相對</t>
+          <t>相對：地球自轉方向是由西向東，站在地面上的我們因為相對運動的關係，看到太陽在天空中呈現由東向西移動的視運動</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>傾斜關鍵</t>
+          <t>傾斜關鍵：四季形成的關鍵在於地軸傾斜造成太陽直射角度隨公轉改變，如果地軸不傾斜，各地全年受光角度幾乎不變，就不會有明顯的四季變化</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>旋轉</t>
+          <t>旋轉：地球自轉使地表輪流面向和背向太陽，造成晝夜交替，這是自轉直接造成的現象</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>繞日</t>
+          <t>繞日：地球公轉搭配地軸傾斜，使太陽直射地表的位置隨季節改變，造成四季變化，這是公轉搭配地軸傾斜共同造成的現象</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>一天</t>
+          <t>一天：地球自轉一圈所需的時間大約是24小時,這就是我們所定義的一天</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>晝長</t>
+          <t>晝長：北半球夏季時,地軸傾向太陽的那一側白天較長、黑夜較短,所以夏季白天比較長</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：地球一邊公轉繞太陽、地軸又傾斜約23.5度，使得地球在公轉軌道不同位置時，太陽直射地表的緯度不同，各地接受到的日照角度與時間長短因此隨季節改變，造成冷熱不均，形成四季</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>相對</t>
+          <t>相對：太陽本身並沒有真的繞著地球移動，是地球由西向東自轉，站在地面上的觀察者因為自身也在運動，才會看到太陽在天空中呈現由東向西移動的樣子，這種因觀察者本身運動造成的表面現象稱為視運動</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>季節</t>
+          <t>季節：夏至時地軸傾向太陽的那一側達到最大程度，太陽直射點位在北回歸線附近，使北半球白天的時間在一年中達到最長</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>自轉</t>
+          <t>自轉：地球是球體，同一時刻太陽只能照亮面向它的那一半，另一半背對太陽的地區照不到陽光，因此地球兩側同時分別是白天和黑夜</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>緯度</t>
+          <t>緯度：緯度越高的地區，因地軸傾斜造成的太陽直射角度隨季節變化幅度越大，四季分明；赤道附近全年太陽直射角度變化較小，四季差異因此較不明顯</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>傾角</t>
+          <t>傾角：地軸大約傾斜23.5度，這個固定的傾角是造成地球四季變化的關鍵因素</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>假設</t>
+          <t>假設：如果地球完全不自轉，同一面會永遠面向太陽而另一面永遠背對太陽，就不會有現在這種約24小時規律的晝夜交替</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：地球自轉決定了短週期(一天內)的晝夜交替；地球公轉搭配地軸傾斜，則決定了長週期(一年內)各季節日照角度與時間長短的變化，兩種運動共同影響地表接受到的日照情況</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>傾斜關鍵</t>
+          <t>傾斜關鍵：四季形成的主要原因是地軸傾斜造成太陽直射角度隨公轉改變,如果地軸不傾斜,各地全年受光角度幾乎不變,就不會有明顯的四季變化</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>相對</t>
+          <t>相對：其實是地球本身在自轉,並不是太陽真的繞著地球跑,但站在地面上的我們感覺像是太陽在天空中移動,這種因為觀察者運動造成的錯覺就叫視運動</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上7-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-1_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>視運動</t>
+          <t>地軸傾斜</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>晝夜</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>一年</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>約23.5度</t>
+          <t>一年</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>公轉</t>
+          <t>自轉</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -723,22 +723,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>地軸傾斜</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>自轉</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>一年</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>不是</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>自轉</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>長</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>視運動</t>
+          <t>由西向東</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>晝夜</t>
+          <t>幾乎沒有</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>地軸傾斜</t>
+          <t>一年</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>視運動</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>幾乎沒有明顯四季</t>
+          <t>由西向東</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>實為地球自轉造成的相對移動</t>
+          <t>自轉</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>由西向東</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>實為地球自轉</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
           <t>無正常晝夜交替</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>太陽直射北半球晝最長</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>一年</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>一年</t>
+          <t>由西向東</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>長</t>
+          <t>視運動</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
